--- a/config/data/SnapshotCapture.xlsx
+++ b/config/data/SnapshotCapture.xlsx
@@ -1,158 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SnapshotCapture" sheetId="1" r:id="rId1"/>
+    <sheet name="SnapshotCapture" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>SnapshotCapture</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@groups</t>
-  </si>
-  <si>
-    <t>common</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>25ad3878c2c338ff</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>owner_identity_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>capture_key</t>
-  </si>
-  <si>
-    <t>subject</t>
-  </si>
-  <si>
-    <t>capture_kind</t>
-  </si>
-  <si>
-    <t>stat</t>
-  </si>
-  <si>
-    <t>resource_kind</t>
-  </si>
-  <si>
-    <t>state_slot_id</t>
-  </si>
-  <si>
-    <t>expression_id</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;ContentIdentity.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>enum&lt;SnapshotSubject&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;SnapshotCaptureKind&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;enum&lt;StatKind&gt;&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;enum&lt;ResourceKind&gt;&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;ref&lt;StateSlot.id&gt;&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;ref&lt;ValueExpression.id&gt;&gt;</t>
-  </si>
-  <si>
-    <t>#groups</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>length=1..120</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F2937"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -222,31 +113,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -534,227 +492,337 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="5" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="32.7109375" style="5" customWidth="1"/>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="23.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" style="5" min="3" max="4"/>
+    <col width="21.7109375" customWidth="1" style="5" min="5" max="5"/>
+    <col width="25.7109375" customWidth="1" style="5" min="6" max="6"/>
+    <col width="24.7109375" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28.7109375" customWidth="1" style="5" min="8" max="8"/>
+    <col width="27.7109375" customWidth="1" style="5" min="9" max="9"/>
+    <col width="32.7109375" customWidth="1" style="5" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>SnapshotCapture</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>25ad3878c2c338ff</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>owner_identity_id</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>capture_key</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>capture_kind</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>resource_kind</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>state_slot_id</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>expression_id</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>18</v>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>owner_identity_id</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>capture_key</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>capture_kind</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>resource_kind</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>state_slot_id</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>expression_id</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>29</v>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>enum&lt;SnapshotSubject&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>enum&lt;SnapshotCaptureKind&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;enum&lt;StatKind&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;enum&lt;ResourceKind&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;ref&lt;StateSlot.id&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;ref&lt;ValueExpression.id&gt;&gt;</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>6</v>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>length=1..120</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" spans="1:10" ht="42" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." sqref="C8:C1007">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Source, Target, Event, Action" promptTitle="SnapshotSubject enum" prompt="Select a value from the dropdown." sqref="E8:E1007">
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Source, Target, Event, Action" promptTitle="SnapshotSubject enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Source,Target,Event,Action"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Stat, Resource, StateSlot, Expression" promptTitle="SnapshotCaptureKind enum" prompt="Select a value from the dropdown." sqref="F8:F1007">
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Stat, Resource, StateSlot, Expression" promptTitle="SnapshotCaptureKind enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Stat,Resource,StateSlot,Expression"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage" promptTitle="StatKind enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
-      <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage"</formula1>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage" promptTitle="StatKind enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage,Elation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource, TeamResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." sqref="H8:H1007">
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource, TeamResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Energy,SkillPoints,Hp,CharacterResource,TeamResource"</formula1>
     </dataValidation>
   </dataValidations>
